--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-untersuchung.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T01:04:27+00:00</t>
+    <t>2026-10-19T02:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -366,10 +366,10 @@
 </t>
   </si>
   <si>
-    <t>Specimen material</t>
-  </si>
-  <si>
-    <t>Examined specimen material. The specimen type is represented via the specimen material and not via pre-coordinated investigation codes.</t>
+    <t>Specimen</t>
+  </si>
+  <si>
+    <t>Specimen examined. The specimen type is represented via the specimen and not via pre-coordinated investigation codes.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchung.Untersuchungszeitpunkt</t>

--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-untersuchung.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T02:33:36+00:00</t>
+    <t>2026-10-19T02:49:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
